--- a/Download/Assets/Resources/4. Data/1. VisualNovel/Dialogs/Dialogs_Day3At.xlsx
+++ b/Download/Assets/Resources/4. Data/1. VisualNovel/Dialogs/Dialogs_Day3At.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dadi2\OneDrive\문서\카카오톡 받은 파일\사운드 다이얼로그\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gksk7\Desktop\Download\Download\Assets\Resources\4. Data\1. VisualNovel\Dialogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B7BFDA-7E18-4A05-8449-EFA4B54C9FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87781FF9-ADAF-46B1-A0E8-914394D76BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" tabRatio="760" activeTab="7" xr2:uid="{49FB8DDA-CC9A-4F10-83A2-6EE5D727B386}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="760" activeTab="7" xr2:uid="{49FB8DDA-CC9A-4F10-83A2-6EE5D727B386}"/>
   </bookViews>
   <sheets>
     <sheet name="S00_11_Fail" sheetId="9" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="285">
   <si>
     <t>dialogType</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2259,6 +2259,18 @@
   </si>
   <si>
     <t>effect</t>
+  </si>
+  <si>
+    <t>EF17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EF26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EF12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3362,9 +3374,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3402,7 +3414,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3508,7 +3520,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3650,7 +3662,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3659,7 +3671,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C8247A8-D7F3-438B-95A1-19D838F3F847}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.25" customWidth="1"/>
     <col min="6" max="6" width="53" customWidth="1"/>
@@ -4314,7 +4326,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2492B5-5286-4C51-A0EE-617DAAF7402C}">
   <dimension ref="A1:R67"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.375" customWidth="1"/>
     <col min="3" max="3" width="9.875" customWidth="1"/>
@@ -4397,7 +4409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="26.05" customHeight="1">
+    <row r="3" spans="1:18" ht="26.1" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4417,7 +4429,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="31.2" customHeight="1">
+    <row r="4" spans="1:18" ht="31.15" customHeight="1">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4437,7 +4449,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="26.05" customHeight="1">
+    <row r="5" spans="1:18" ht="26.1" customHeight="1">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4503,7 +4515,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="28.2" customHeight="1">
+    <row r="8" spans="1:18" ht="28.15" customHeight="1">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4523,7 +4535,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="29.95" customHeight="1">
+    <row r="9" spans="1:18" ht="30" customHeight="1">
       <c r="A9">
         <v>1</v>
       </c>
@@ -4893,7 +4905,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB6832A-6597-4EBE-A642-50EFC6AE260A}">
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="6.375" customWidth="1"/>
     <col min="5" max="5" width="16.125" customWidth="1"/>
@@ -5283,7 +5295,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E4D3827-FA20-492E-9CAA-498828664590}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.375" customWidth="1"/>
     <col min="6" max="6" width="52.75" customWidth="1"/>
@@ -5709,7 +5721,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{912E2E5F-C23B-4F25-A39B-FF9BDCB35635}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="90" customWidth="1"/>
@@ -6313,7 +6325,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D57870A9-ECB4-4291-BFAF-986814B662D2}">
   <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.5" customWidth="1"/>
     <col min="6" max="6" width="76.75" customWidth="1"/>
@@ -6598,8 +6610,8 @@
       <c r="H14" t="s">
         <v>225</v>
       </c>
-      <c r="J14">
-        <v>17</v>
+      <c r="J14" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -6725,7 +6737,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="24.25">
+    <row r="21" spans="1:10" ht="25.5">
       <c r="A21">
         <v>1</v>
       </c>
@@ -6907,8 +6919,8 @@
       <c r="H29" t="s">
         <v>224</v>
       </c>
-      <c r="J29">
-        <v>26</v>
+      <c r="J29" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -6990,7 +7002,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14DD822B-AB3F-4083-911C-110C08E3FDA4}">
   <dimension ref="A1:R40"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.5" customWidth="1"/>
     <col min="6" max="6" width="55.5" customWidth="1"/>
@@ -7171,7 +7183,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="24.25">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>1</v>
       </c>
@@ -7276,7 +7288,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="24.25">
+    <row r="15" spans="1:18" ht="25.5">
       <c r="A15">
         <v>1</v>
       </c>
@@ -7415,7 +7427,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="24.25">
+    <row r="23" spans="1:10" ht="25.5">
       <c r="A23">
         <v>1</v>
       </c>
@@ -7560,7 +7572,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="24.25">
+    <row r="31" spans="1:10">
       <c r="A31">
         <v>1</v>
       </c>
@@ -7702,7 +7714,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="24.25">
+    <row r="39" spans="1:9" ht="25.5">
       <c r="A39">
         <v>1</v>
       </c>
@@ -7778,7 +7790,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1151488-0F44-491C-8515-0B5CDD067839}">
   <dimension ref="A1:R87"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
     <col min="2" max="2" width="10.875" customWidth="1"/>
@@ -8265,7 +8277,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="24.25">
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>1</v>
       </c>
@@ -8884,7 +8896,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="96.95">
+    <row r="56" spans="1:10" ht="89.25">
       <c r="A56">
         <v>1</v>
       </c>
@@ -9272,8 +9284,8 @@
       <c r="H74" t="s">
         <v>235</v>
       </c>
-      <c r="J74">
-        <v>12</v>
+      <c r="J74" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -9359,7 +9371,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="48.5">
+    <row r="79" spans="1:10" ht="38.25">
       <c r="A79">
         <v>1</v>
       </c>
@@ -9398,8 +9410,8 @@
       <c r="H80" t="s">
         <v>235</v>
       </c>
-      <c r="J80">
-        <v>12</v>
+      <c r="J80" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="81" spans="1:18">
@@ -9421,11 +9433,11 @@
       <c r="H81" t="s">
         <v>235</v>
       </c>
-      <c r="J81">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18" ht="96.95">
+      <c r="J81" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="96">
       <c r="A82">
         <v>1</v>
       </c>
